--- a/aggregate/raw_kmeans/aggregate_kmeans_numeric.xlsx
+++ b/aggregate/raw_kmeans/aggregate_kmeans_numeric.xlsx
@@ -27,9 +27,30 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="34">
   <si>
     <t>model</t>
+  </si>
+  <si>
+    <t>clusters</t>
+  </si>
+  <si>
+    <t>rounds_mean</t>
+  </si>
+  <si>
+    <t>rounds_std</t>
+  </si>
+  <si>
+    <t>tol_mean</t>
+  </si>
+  <si>
+    <t>tol_std</t>
+  </si>
+  <si>
+    <t>iteration_mean</t>
+  </si>
+  <si>
+    <t>iteration_std</t>
   </si>
   <si>
     <t>ARI_mean</t>
@@ -121,14 +142,7 @@
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="176" formatCode="0.000_ "/>
   </numFmts>
-  <fonts count="21">
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
+  <fonts count="20">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -599,148 +613,148 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1095,16 +1109,22 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:U7"/>
+  <dimension ref="A1:AB7"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="6"/>
   <cols>
-    <col min="1" max="1" width="28.3333333333333" customWidth="1"/>
-    <col min="2" max="17" width="12.8888888888889"/>
-    <col min="18" max="18" width="13"/>
-    <col min="19" max="21" width="12.8888888888889"/>
+    <col min="1" max="1" width="26.1111111111111" customWidth="1"/>
+    <col min="2" max="2" width="25.8888888888889" hidden="1" customWidth="1"/>
+    <col min="3" max="3" width="21.5555555555556" hidden="1" customWidth="1"/>
+    <col min="4" max="4" width="18.1111111111111" hidden="1" customWidth="1"/>
+    <col min="5" max="5" width="15.6666666666667" hidden="1" customWidth="1"/>
+    <col min="6" max="7" width="9" hidden="1" customWidth="1"/>
+    <col min="8" max="8" width="12.8888888888889" hidden="1" customWidth="1"/>
+    <col min="9" max="24" width="12.8888888888889"/>
+    <col min="25" max="25" width="13"/>
+    <col min="26" max="28" width="12.8888888888889"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21">
+    <row r="1" spans="1:28">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1168,395 +1188,542 @@
       <c r="U1" s="1" t="s">
         <v>20</v>
       </c>
+      <c r="V1" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="W1" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="X1" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="Y1" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="Z1" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="AA1" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AB1" s="1" t="s">
+        <v>27</v>
+      </c>
     </row>
-    <row r="2" spans="1:21">
+    <row r="2" spans="1:28">
       <c r="A2" s="1" t="s">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="B2" s="1">
-        <v>0.45600985898205</v>
+        <v>35.1818181818182</v>
       </c>
       <c r="C2" s="1">
-        <v>0.0392768143718224</v>
+        <v>225.181818181818</v>
       </c>
       <c r="D2" s="1">
-        <v>0.628307555159137</v>
+        <v>0</v>
       </c>
       <c r="E2" s="1">
-        <v>0.020942692129945</v>
+        <v>0.005</v>
       </c>
       <c r="F2" s="1">
-        <v>3.42362637490397</v>
+        <v>0</v>
       </c>
       <c r="G2" s="1">
-        <v>0.106216875402474</v>
+        <v>14.5</v>
       </c>
       <c r="H2" s="1">
-        <v>454.379300607445</v>
+        <v>8.8034084308295</v>
       </c>
       <c r="I2" s="1">
-        <v>15.093506578964</v>
+        <v>0.455872361491109</v>
       </c>
       <c r="J2" s="1">
-        <v>0.589118091858368</v>
+        <v>0.0393280807466873</v>
       </c>
       <c r="K2" s="1">
-        <v>0.0428784376470436</v>
+        <v>0.62825661734593</v>
       </c>
       <c r="L2" s="1">
-        <v>0.601403430104055</v>
+        <v>0.0208974418496894</v>
       </c>
       <c r="M2" s="1">
-        <v>0.0466078405943606</v>
+        <v>3.42447198353551</v>
       </c>
       <c r="N2" s="1">
-        <v>0.589118091858368</v>
+        <v>0.105839255093438</v>
       </c>
       <c r="O2" s="1">
-        <v>0.0428784376470436</v>
+        <v>454.336115515589</v>
       </c>
       <c r="P2" s="1">
-        <v>0.682038785018445</v>
+        <v>15.084984005928</v>
       </c>
       <c r="Q2" s="1">
-        <v>0.0455152613786044</v>
+        <v>0.588956379113834</v>
       </c>
       <c r="R2" s="1">
-        <v>15457.8832585653</v>
+        <v>0.0428559866048834</v>
       </c>
       <c r="S2" s="1">
-        <v>56.3119299154047</v>
+        <v>0.601227842257868</v>
       </c>
       <c r="T2" s="1">
-        <v>1.08611930572625</v>
+        <v>0.0466348881688412</v>
       </c>
       <c r="U2" s="1">
-        <v>0.425581492110557</v>
+        <v>0.588956379113834</v>
+      </c>
+      <c r="V2" s="1">
+        <v>0.0428559866048834</v>
+      </c>
+      <c r="W2" s="1">
+        <v>0.681953379157372</v>
+      </c>
+      <c r="X2" s="1">
+        <v>0.0455153273702558</v>
+      </c>
+      <c r="Y2" s="1">
+        <v>15458.127028263</v>
+      </c>
+      <c r="Z2" s="1">
+        <v>56.2572171271332</v>
+      </c>
+      <c r="AA2" s="1">
+        <v>1.31486658833244</v>
+      </c>
+      <c r="AB2" s="1">
+        <v>0.457571688347979</v>
       </c>
     </row>
-    <row r="3" spans="1:21">
+    <row r="3" spans="1:28">
       <c r="A3" s="1" t="s">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="B3" s="1">
-        <v>0.470909954848026</v>
+        <v>35.1818181818182</v>
       </c>
       <c r="C3" s="1">
-        <v>0.0419004273187351</v>
+        <v>225.181818181818</v>
       </c>
       <c r="D3" s="1">
-        <v>0.639439150790965</v>
+        <v>0</v>
       </c>
       <c r="E3" s="1">
-        <v>0.0242871581426995</v>
+        <v>0.005</v>
       </c>
       <c r="F3" s="1">
-        <v>3.46692847307593</v>
+        <v>0</v>
       </c>
       <c r="G3" s="1">
-        <v>0.124758959823643</v>
+        <v>14.5</v>
       </c>
       <c r="H3" s="1">
-        <v>435.41567348508</v>
+        <v>8.8034084308295</v>
       </c>
       <c r="I3" s="1">
-        <v>22.7407885569169</v>
+        <v>0.470829793393274</v>
       </c>
       <c r="J3" s="1">
-        <v>0.599407242780788</v>
+        <v>0.0419345428678855</v>
       </c>
       <c r="K3" s="1">
-        <v>0.0418048243337868</v>
+        <v>0.63938974987403</v>
       </c>
       <c r="L3" s="1">
-        <v>0.611029313617124</v>
+        <v>0.0242905476153454</v>
       </c>
       <c r="M3" s="1">
-        <v>0.0454390234835416</v>
+        <v>3.46684483598603</v>
       </c>
       <c r="N3" s="1">
-        <v>0.599407242780788</v>
+        <v>0.124680053292772</v>
       </c>
       <c r="O3" s="1">
-        <v>0.0418048243337868</v>
+        <v>435.407079894565</v>
       </c>
       <c r="P3" s="1">
-        <v>0.68879338968088</v>
+        <v>22.7457253220752</v>
       </c>
       <c r="Q3" s="1">
-        <v>0.0439904490552412</v>
+        <v>0.599388261337878</v>
       </c>
       <c r="R3" s="1">
-        <v>15724.4033152262</v>
+        <v>0.0417943992898243</v>
       </c>
       <c r="S3" s="1">
-        <v>75.3117668090387</v>
+        <v>0.611017262845023</v>
       </c>
       <c r="T3" s="1">
-        <v>1.01737106207645</v>
+        <v>0.0454252709917023</v>
       </c>
       <c r="U3" s="1">
-        <v>0.0429839432607639</v>
+        <v>0.599388261337878</v>
+      </c>
+      <c r="V3" s="1">
+        <v>0.0417943992898243</v>
+      </c>
+      <c r="W3" s="1">
+        <v>0.688818292874712</v>
+      </c>
+      <c r="X3" s="1">
+        <v>0.0439984049332764</v>
+      </c>
+      <c r="Y3" s="1">
+        <v>15724.4731622869</v>
+      </c>
+      <c r="Z3" s="1">
+        <v>75.3552985039599</v>
+      </c>
+      <c r="AA3" s="1">
+        <v>1.22719647956617</v>
+      </c>
+      <c r="AB3" s="1">
+        <v>0.0541824414211957</v>
       </c>
     </row>
-    <row r="4" spans="1:21">
+    <row r="4" spans="1:28">
       <c r="A4" s="1" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="B4" s="1">
-        <v>0.481055225795001</v>
+        <v>35.1818181818182</v>
       </c>
       <c r="C4" s="1">
-        <v>0.0396763044879732</v>
+        <v>225.181818181818</v>
       </c>
       <c r="D4" s="1">
-        <v>0.651638218141928</v>
+        <v>0</v>
       </c>
       <c r="E4" s="1">
-        <v>0.0206763424673785</v>
+        <v>0.005</v>
       </c>
       <c r="F4" s="1">
-        <v>3.38915675039012</v>
+        <v>0</v>
       </c>
       <c r="G4" s="1">
-        <v>0.0946927719085</v>
+        <v>14.5</v>
       </c>
       <c r="H4" s="1">
-        <v>415.428028201588</v>
+        <v>8.8034084308295</v>
       </c>
       <c r="I4" s="1">
-        <v>14.7326914449156</v>
+        <v>0.48102160868673</v>
       </c>
       <c r="J4" s="1">
-        <v>0.601844443853113</v>
+        <v>0.0396776760417248</v>
       </c>
       <c r="K4" s="1">
-        <v>0.042875563545436</v>
+        <v>0.651618232306291</v>
       </c>
       <c r="L4" s="1">
-        <v>0.611935197821202</v>
+        <v>0.0206963533664281</v>
       </c>
       <c r="M4" s="1">
-        <v>0.0470562348173726</v>
+        <v>3.3893293125723</v>
       </c>
       <c r="N4" s="1">
-        <v>0.601844443853113</v>
+        <v>0.0947638676377075</v>
       </c>
       <c r="O4" s="1">
-        <v>0.042875563545436</v>
+        <v>415.42560331285</v>
       </c>
       <c r="P4" s="1">
-        <v>0.693633891947766</v>
+        <v>14.7324484936165</v>
       </c>
       <c r="Q4" s="1">
-        <v>0.0453261757145516</v>
+        <v>0.60183686330401</v>
       </c>
       <c r="R4" s="1">
-        <v>15855.0945881237</v>
+        <v>0.0428725817027125</v>
       </c>
       <c r="S4" s="1">
-        <v>53.9137280664892</v>
+        <v>0.611935358773613</v>
       </c>
       <c r="T4" s="1">
-        <v>2.01697150288206</v>
+        <v>0.0470648593443694</v>
       </c>
       <c r="U4" s="1">
-        <v>0.142280382348254</v>
+        <v>0.60183686330401</v>
+      </c>
+      <c r="V4" s="1">
+        <v>0.0428725817027125</v>
+      </c>
+      <c r="W4" s="1">
+        <v>0.693641654649551</v>
+      </c>
+      <c r="X4" s="1">
+        <v>0.0453432088511664</v>
+      </c>
+      <c r="Y4" s="1">
+        <v>15855.1139815822</v>
+      </c>
+      <c r="Z4" s="1">
+        <v>53.9099157247143</v>
+      </c>
+      <c r="AA4" s="1">
+        <v>2.32085394353578</v>
+      </c>
+      <c r="AB4" s="1">
+        <v>0.117632345971122</v>
       </c>
     </row>
-    <row r="5" spans="1:21">
+    <row r="5" spans="1:28">
       <c r="A5" s="1" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="B5" s="1">
-        <v>0.500809065696986</v>
+        <v>35.1818181818182</v>
       </c>
       <c r="C5" s="1">
-        <v>0.048298622619204</v>
+        <v>225.181818181818</v>
       </c>
       <c r="D5" s="1">
-        <v>0.671038171368105</v>
+        <v>0</v>
       </c>
       <c r="E5" s="1">
-        <v>0.0242904212191941</v>
+        <v>0.005</v>
       </c>
       <c r="F5" s="1">
-        <v>3.68790071976184</v>
+        <v>0</v>
       </c>
       <c r="G5" s="1">
-        <v>0.164484637565075</v>
+        <v>14.5</v>
       </c>
       <c r="H5" s="1">
-        <v>439.42368044439</v>
+        <v>8.8034084308295</v>
       </c>
       <c r="I5" s="1">
-        <v>22.6937213429301</v>
+        <v>0.500800536275101</v>
       </c>
       <c r="J5" s="1">
-        <v>0.614969161941971</v>
+        <v>0.0482884979951939</v>
       </c>
       <c r="K5" s="1">
-        <v>0.0505250165046424</v>
+        <v>0.671015924266774</v>
       </c>
       <c r="L5" s="1">
-        <v>0.62398658617751</v>
+        <v>0.0242790698699166</v>
       </c>
       <c r="M5" s="1">
-        <v>0.0542453774845121</v>
+        <v>3.68797936492509</v>
       </c>
       <c r="N5" s="1">
-        <v>0.614969161941971</v>
+        <v>0.164488630360686</v>
       </c>
       <c r="O5" s="1">
-        <v>0.0505250165046424</v>
+        <v>439.422666167983</v>
       </c>
       <c r="P5" s="1">
-        <v>0.700098095183813</v>
+        <v>22.6922821361057</v>
       </c>
       <c r="Q5" s="1">
-        <v>0.0524410696959924</v>
+        <v>0.614960042015421</v>
       </c>
       <c r="R5" s="1">
-        <v>4441.28234702601</v>
+        <v>0.0505201586611573</v>
       </c>
       <c r="S5" s="1">
-        <v>21.3217531098904</v>
+        <v>0.623974302336557</v>
       </c>
       <c r="T5" s="1">
-        <v>1.94928282463189</v>
+        <v>0.0542294622932467</v>
       </c>
       <c r="U5" s="1">
-        <v>0.108205664192818</v>
+        <v>0.614960042015421</v>
+      </c>
+      <c r="V5" s="1">
+        <v>0.0505201586611573</v>
+      </c>
+      <c r="W5" s="1">
+        <v>0.700066054669293</v>
+      </c>
+      <c r="X5" s="1">
+        <v>0.0524148452997994</v>
+      </c>
+      <c r="Y5" s="1">
+        <v>4441.28475481669</v>
+      </c>
+      <c r="Z5" s="1">
+        <v>21.3169260520808</v>
+      </c>
+      <c r="AA5" s="1">
+        <v>2.1134751290986</v>
+      </c>
+      <c r="AB5" s="1">
+        <v>0.154569833690886</v>
       </c>
     </row>
-    <row r="6" spans="1:21">
+    <row r="6" spans="1:28">
       <c r="A6" s="1" t="s">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="B6" s="1">
-        <v>0.452858123771022</v>
+        <v>35.1818181818182</v>
       </c>
       <c r="C6" s="1">
-        <v>0.0357925804705278</v>
+        <v>225.181818181818</v>
       </c>
       <c r="D6" s="1">
-        <v>0.621473037788297</v>
+        <v>0</v>
       </c>
       <c r="E6" s="1">
-        <v>0.0213993319257408</v>
+        <v>0.005</v>
       </c>
       <c r="F6" s="1">
-        <v>3.58978180782506</v>
+        <v>0</v>
       </c>
       <c r="G6" s="1">
-        <v>0.124980345865403</v>
+        <v>14.5</v>
       </c>
       <c r="H6" s="1">
-        <v>497.548271437429</v>
+        <v>8.8034084308295</v>
       </c>
       <c r="I6" s="1">
-        <v>20.1237926096881</v>
+        <v>0.45286461166416</v>
       </c>
       <c r="J6" s="1">
-        <v>0.592817144583926</v>
+        <v>0.0357908335984691</v>
       </c>
       <c r="K6" s="1">
-        <v>0.0395538858688648</v>
+        <v>0.621469637342191</v>
       </c>
       <c r="L6" s="1">
-        <v>0.608732052341881</v>
+        <v>0.0213931924557906</v>
       </c>
       <c r="M6" s="1">
-        <v>0.0425726449090291</v>
+        <v>3.58981409427291</v>
       </c>
       <c r="N6" s="1">
-        <v>0.592817144583926</v>
+        <v>0.124922211341082</v>
       </c>
       <c r="O6" s="1">
-        <v>0.0395538858688648</v>
+        <v>497.547556884405</v>
       </c>
       <c r="P6" s="1">
-        <v>0.692951430671917</v>
+        <v>20.1238996275824</v>
       </c>
       <c r="Q6" s="1">
-        <v>0.0413817454732602</v>
+        <v>0.592820881768179</v>
       </c>
       <c r="R6" s="1">
-        <v>10234.2178658688</v>
+        <v>0.0395478093878475</v>
       </c>
       <c r="S6" s="1">
-        <v>39.4908701667803</v>
+        <v>0.608729859515215</v>
       </c>
       <c r="T6" s="1">
-        <v>2.11387748862758</v>
+        <v>0.0425763510908645</v>
       </c>
       <c r="U6" s="1">
-        <v>0.211332358017305</v>
+        <v>0.592820881768179</v>
+      </c>
+      <c r="V6" s="1">
+        <v>0.0395478093878475</v>
+      </c>
+      <c r="W6" s="1">
+        <v>0.692947530458533</v>
+      </c>
+      <c r="X6" s="1">
+        <v>0.0413884852819212</v>
+      </c>
+      <c r="Y6" s="1">
+        <v>10234.2214401245</v>
+      </c>
+      <c r="Z6" s="1">
+        <v>39.4918869446912</v>
+      </c>
+      <c r="AA6" s="1">
+        <v>2.1163741386298</v>
+      </c>
+      <c r="AB6" s="1">
+        <v>0.119005540867058</v>
       </c>
     </row>
-    <row r="7" spans="1:21">
+    <row r="7" spans="1:28">
       <c r="A7" s="1" t="s">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="B7" s="1">
-        <v>0.324642105944552</v>
+        <v>35.1818181818182</v>
       </c>
       <c r="C7" s="1">
-        <v>0.0250446812101909</v>
+        <v>225.181818181818</v>
       </c>
       <c r="D7" s="1">
-        <v>0.511190726433019</v>
+        <v>0</v>
       </c>
       <c r="E7" s="1">
-        <v>0.0189900890005627</v>
+        <v>0.005</v>
       </c>
       <c r="F7" s="1">
-        <v>3.19303573066083</v>
+        <v>0</v>
       </c>
       <c r="G7" s="1">
-        <v>0.0956845443839288</v>
+        <v>14.5</v>
       </c>
       <c r="H7" s="1">
-        <v>442.262004836743</v>
+        <v>8.8034084308295</v>
       </c>
       <c r="I7" s="1">
-        <v>21.3907502300927</v>
+        <v>0.324590707470854</v>
       </c>
       <c r="J7" s="1">
-        <v>0.495963132780005</v>
+        <v>0.0248171194527472</v>
       </c>
       <c r="K7" s="1">
-        <v>0.0286979960856207</v>
+        <v>0.511121152986011</v>
       </c>
       <c r="L7" s="1">
-        <v>0.504646720613951</v>
+        <v>0.0188999874151599</v>
       </c>
       <c r="M7" s="1">
-        <v>0.0335161880410306</v>
+        <v>3.19587629518585</v>
       </c>
       <c r="N7" s="1">
-        <v>0.495963132780005</v>
+        <v>0.0986315510979267</v>
       </c>
       <c r="O7" s="1">
-        <v>0.0286979960856207</v>
+        <v>442.049441465606</v>
       </c>
       <c r="P7" s="1">
-        <v>0.58934584042856</v>
+        <v>21.5143600727445</v>
       </c>
       <c r="Q7" s="1">
-        <v>0.0419345636069133</v>
+        <v>0.495837471255419</v>
       </c>
       <c r="R7" s="1">
-        <v>267614.169401966</v>
+        <v>0.0285526982741324</v>
       </c>
       <c r="S7" s="1">
-        <v>1255.1903546009</v>
+        <v>0.504524255539107</v>
       </c>
       <c r="T7" s="1">
-        <v>1.06049012993321</v>
+        <v>0.033359171423976</v>
       </c>
       <c r="U7" s="1">
-        <v>0.0451149022377641</v>
+        <v>0.495837471255419</v>
+      </c>
+      <c r="V7" s="1">
+        <v>0.0285526982741324</v>
+      </c>
+      <c r="W7" s="1">
+        <v>0.589098067037226</v>
+      </c>
+      <c r="X7" s="1">
+        <v>0.0417385001879282</v>
+      </c>
+      <c r="Y7" s="1">
+        <v>267637.205799635</v>
+      </c>
+      <c r="Z7" s="1">
+        <v>1265.88546290685</v>
+      </c>
+      <c r="AA7" s="1">
+        <v>1.28717808795698</v>
+      </c>
+      <c r="AB7" s="1">
+        <v>0.18963578611368</v>
       </c>
     </row>
   </sheetData>
